--- a/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
+++ b/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BDC944-5B28-4325-8B2E-3884F45C6BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755884B9-FA0B-435A-80C6-6DDFFE068A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Báo cáo QC" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>VIKING VIETNAM CO.,LTD</t>
   </si>
@@ -80,115 +93,7 @@
     <t>Ký tên</t>
   </si>
   <si>
-    <t>28/05/2026</t>
-  </si>
-  <si>
-    <t>L/40</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Diễu không đều / Uneven Stitching | Sụp mí /Run-off stitching</t>
-  </si>
-  <si>
-    <t>L/2/20</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>Công nhân không cẩn thận  - sửa</t>
-  </si>
-  <si>
-    <t>Đạt</t>
-  </si>
-  <si>
-    <t>M/40</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nhăn, nhíu, vặn / Wrinkles, Creases, Twisted seam</t>
-  </si>
-  <si>
-    <t>M/1/10</t>
-  </si>
-  <si>
-    <t>Tổng kiểm: 30 | Tổng lỗi: 3</t>
-  </si>
-  <si>
-    <t>10.00%</t>
-  </si>
-  <si>
-    <t>27/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nhăn, nhíu, vặn / Wrinkles, Creases, Twisted seam | Thiếu lót, giật lót =&amp;gt; đùn / Lining width or length is shorter than outer</t>
-  </si>
-  <si>
-    <t>L/4/20</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>Công nhân không  cẩn thận  - sửa</t>
-  </si>
-  <si>
-    <t>Chưa ký</t>
-  </si>
-  <si>
-    <t>Tổng kiểm: 20 | Tổng lỗi: 4</t>
-  </si>
-  <si>
-    <t>20.00%</t>
-  </si>
-  <si>
-    <t>26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Không đối xứng / Unsymmetrical | Le mí</t>
-  </si>
-  <si>
-    <t>Tổng kiểm: 20 | Tổng lỗi: 2</t>
-  </si>
-  <si>
-    <t>25/05/2026</t>
-  </si>
-  <si>
-    <t>2XL/20</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thiếu, dư nhãn, logo /Missing/extra label,logo</t>
-  </si>
-  <si>
-    <t>2XL/1/20</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>Công nhân không cẩn thận  -sửa</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>3XL/5</t>
-  </si>
-  <si>
-    <t>3XL/1/5</t>
-  </si>
-  <si>
-    <t>Tổng kiểm: 25 | Tổng lỗi: 2</t>
-  </si>
-  <si>
-    <t>8.00%</t>
-  </si>
-  <si>
     <t>TỔNG TOÀN BẢNG</t>
-  </si>
-  <si>
-    <t>Tổng kiểm: 95 | Tổng lỗi: 11</t>
-  </si>
-  <si>
-    <t>11.58%</t>
   </si>
 </sst>
 </file>
@@ -199,7 +104,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -207,41 +112,48 @@
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -258,7 +170,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -301,12 +214,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -316,14 +237,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,123 +287,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1143000" cy="381000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12144375" y="1600200"/>
-          <a:ext cx="1143000" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1143000" cy="381000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12172950" y="3190875"/>
-          <a:ext cx="1143000" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1143000" cy="381000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12134850" y="3724275"/>
-          <a:ext cx="1143000" cy="381000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -825,40 +621,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.375" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:10" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="9" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="3" spans="1:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J1" s="13"/>
+    </row>
+    <row r="3" spans="1:10" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -879,7 +675,7 @@
       </c>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -894,7 +690,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -926,333 +722,147 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="11" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="9">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J14:J16"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:J1"/>

--- a/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
+++ b/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755884B9-FA0B-435A-80C6-6DDFFE068A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCDF95F-6F0F-4DFB-B81B-C0200FAE214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Báo cáo QC" sheetId="1" r:id="rId1"/>
@@ -152,8 +152,8 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -220,9 +220,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -237,9 +234,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -621,76 +621,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="28.36328125" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" customWidth="1"/>
+    <col min="7" max="7" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J1" s="12"/>
+    </row>
+    <row r="3" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="10"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -722,7 +722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="5"/>
       <c r="C7" s="4"/>
@@ -734,7 +734,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
       <c r="C8" s="4"/>
@@ -746,19 +746,19 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="13"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
@@ -770,19 +770,19 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
@@ -794,19 +794,19 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="5"/>
       <c r="C14" s="4"/>
@@ -818,7 +818,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4"/>
@@ -830,33 +830,33 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
+++ b/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCDF95F-6F0F-4DFB-B81B-C0200FAE214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A03034E-B589-4AB2-9829-326989DCD161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -220,6 +220,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -235,7 +238,7 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,59 +639,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="12"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="3" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -725,43 +728,42 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
-      <c r="C8" s="4"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="4"/>
       <c r="E8" s="3"/>
       <c r="F8" s="4"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="5"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="4"/>
@@ -771,21 +773,21 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="4"/>
@@ -795,68 +797,68 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="4"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="4"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="4"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="3"/>
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="5"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
+++ b/data/templates/BaoCao_InLineQC_All_1780023089422.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A03034E-B589-4AB2-9829-326989DCD161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F405D55-CF47-463C-B6D2-D5EF4D9FC0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,6 +223,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -236,9 +239,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,65 +633,65 @@
     <col min="5" max="5" width="28.36328125" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="14.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="13"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="3" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="10"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -752,7 +752,7 @@
       <c r="A9" s="7"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="14"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -776,7 +776,7 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="14"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -800,7 +800,7 @@
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="14"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -836,7 +836,7 @@
       <c r="A16" s="7"/>
       <c r="B16" s="5"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="14"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -845,20 +845,20 @@
       <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="9">
